--- a/tests/data.xlsx
+++ b/tests/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y9798\Desktop\excel-agent\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y9798\Desktop\excel-agent\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDCCEA9-456D-492F-8090-F88B775943CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DF9A7E-A046-4E06-9C18-D52BC8C6EAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D492"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.59765625" customWidth="1"/>
@@ -474,6 +474,6782 @@
         <v>6</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B9">
+        <v>1221</v>
+      </c>
+      <c r="C9">
+        <v>1122</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
+        <v>46186</v>
+      </c>
+      <c r="B10">
+        <v>1221</v>
+      </c>
+      <c r="C10">
+        <v>1122</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B11">
+        <v>1221</v>
+      </c>
+      <c r="C11">
+        <v>1122</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B12">
+        <v>1221</v>
+      </c>
+      <c r="C12">
+        <v>1122</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B13">
+        <v>1221</v>
+      </c>
+      <c r="C13">
+        <v>1122</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B14">
+        <v>1221</v>
+      </c>
+      <c r="C14">
+        <v>1122</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B15">
+        <v>1221</v>
+      </c>
+      <c r="C15">
+        <v>1122</v>
+      </c>
+      <c r="D15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B16">
+        <v>1221</v>
+      </c>
+      <c r="C16">
+        <v>1122</v>
+      </c>
+      <c r="D16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B17">
+        <v>1221</v>
+      </c>
+      <c r="C17">
+        <v>1122</v>
+      </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B18">
+        <v>1221</v>
+      </c>
+      <c r="C18">
+        <v>1122</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B19">
+        <v>1221</v>
+      </c>
+      <c r="C19">
+        <v>1122</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B20">
+        <v>1221</v>
+      </c>
+      <c r="C20">
+        <v>1122</v>
+      </c>
+      <c r="D20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B21">
+        <v>1221</v>
+      </c>
+      <c r="C21">
+        <v>1122</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B22">
+        <v>1221</v>
+      </c>
+      <c r="C22">
+        <v>1122</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B23">
+        <v>1221</v>
+      </c>
+      <c r="C23">
+        <v>1122</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B24">
+        <v>1221</v>
+      </c>
+      <c r="C24">
+        <v>1122</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B25">
+        <v>1221</v>
+      </c>
+      <c r="C25">
+        <v>1122</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B26">
+        <v>1221</v>
+      </c>
+      <c r="C26">
+        <v>1122</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B27">
+        <v>1221</v>
+      </c>
+      <c r="C27">
+        <v>1122</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B28">
+        <v>1221</v>
+      </c>
+      <c r="C28">
+        <v>1122</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B29">
+        <v>1221</v>
+      </c>
+      <c r="C29">
+        <v>1122</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B30">
+        <v>1221</v>
+      </c>
+      <c r="C30">
+        <v>1122</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B31">
+        <v>1221</v>
+      </c>
+      <c r="C31">
+        <v>1122</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B32">
+        <v>1221</v>
+      </c>
+      <c r="C32">
+        <v>1122</v>
+      </c>
+      <c r="D32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B33">
+        <v>1221</v>
+      </c>
+      <c r="C33">
+        <v>1122</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B34">
+        <v>1221</v>
+      </c>
+      <c r="C34">
+        <v>1122</v>
+      </c>
+      <c r="D34">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B35">
+        <v>1221</v>
+      </c>
+      <c r="C35">
+        <v>1122</v>
+      </c>
+      <c r="D35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B36">
+        <v>1221</v>
+      </c>
+      <c r="C36">
+        <v>1122</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B37">
+        <v>1221</v>
+      </c>
+      <c r="C37">
+        <v>1122</v>
+      </c>
+      <c r="D37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B38">
+        <v>1221</v>
+      </c>
+      <c r="C38">
+        <v>1122</v>
+      </c>
+      <c r="D38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B39">
+        <v>1221</v>
+      </c>
+      <c r="C39">
+        <v>1122</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B40">
+        <v>1221</v>
+      </c>
+      <c r="C40">
+        <v>1122</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B41">
+        <v>1221</v>
+      </c>
+      <c r="C41">
+        <v>1122</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B42">
+        <v>1221</v>
+      </c>
+      <c r="C42">
+        <v>1122</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B43">
+        <v>1221</v>
+      </c>
+      <c r="C43">
+        <v>1122</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B44">
+        <v>1221</v>
+      </c>
+      <c r="C44">
+        <v>1122</v>
+      </c>
+      <c r="D44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B45">
+        <v>1221</v>
+      </c>
+      <c r="C45">
+        <v>1122</v>
+      </c>
+      <c r="D45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B46">
+        <v>1221</v>
+      </c>
+      <c r="C46">
+        <v>1122</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B47">
+        <v>1221</v>
+      </c>
+      <c r="C47">
+        <v>1122</v>
+      </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B48">
+        <v>1221</v>
+      </c>
+      <c r="C48">
+        <v>1122</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A49" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B49">
+        <v>1221</v>
+      </c>
+      <c r="C49">
+        <v>1122</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A50" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B50">
+        <v>1221</v>
+      </c>
+      <c r="C50">
+        <v>1122</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A51" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B51">
+        <v>1221</v>
+      </c>
+      <c r="C51">
+        <v>1122</v>
+      </c>
+      <c r="D51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A52" s="1">
+        <v>46228</v>
+      </c>
+      <c r="B52">
+        <v>1221</v>
+      </c>
+      <c r="C52">
+        <v>1122</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A53" s="1">
+        <v>46229</v>
+      </c>
+      <c r="B53">
+        <v>1221</v>
+      </c>
+      <c r="C53">
+        <v>1122</v>
+      </c>
+      <c r="D53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A54" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B54">
+        <v>1221</v>
+      </c>
+      <c r="C54">
+        <v>1122</v>
+      </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A55" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B55">
+        <v>1221</v>
+      </c>
+      <c r="C55">
+        <v>1122</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A56" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B56">
+        <v>1221</v>
+      </c>
+      <c r="C56">
+        <v>1122</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A57" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B57">
+        <v>1221</v>
+      </c>
+      <c r="C57">
+        <v>1122</v>
+      </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B58">
+        <v>1221</v>
+      </c>
+      <c r="C58">
+        <v>1122</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A59" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B59">
+        <v>1221</v>
+      </c>
+      <c r="C59">
+        <v>1122</v>
+      </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A60" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B60">
+        <v>1221</v>
+      </c>
+      <c r="C60">
+        <v>1122</v>
+      </c>
+      <c r="D60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A61" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B61">
+        <v>1221</v>
+      </c>
+      <c r="C61">
+        <v>1122</v>
+      </c>
+      <c r="D61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B62">
+        <v>1221</v>
+      </c>
+      <c r="C62">
+        <v>1122</v>
+      </c>
+      <c r="D62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A63" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B63">
+        <v>1221</v>
+      </c>
+      <c r="C63">
+        <v>1122</v>
+      </c>
+      <c r="D63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B64">
+        <v>1221</v>
+      </c>
+      <c r="C64">
+        <v>1122</v>
+      </c>
+      <c r="D64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A65" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B65">
+        <v>1221</v>
+      </c>
+      <c r="C65">
+        <v>1122</v>
+      </c>
+      <c r="D65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="1">
+        <v>46242</v>
+      </c>
+      <c r="B66">
+        <v>1221</v>
+      </c>
+      <c r="C66">
+        <v>1122</v>
+      </c>
+      <c r="D66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="1">
+        <v>46243</v>
+      </c>
+      <c r="B67">
+        <v>1221</v>
+      </c>
+      <c r="C67">
+        <v>1122</v>
+      </c>
+      <c r="D67">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B68">
+        <v>1221</v>
+      </c>
+      <c r="C68">
+        <v>1122</v>
+      </c>
+      <c r="D68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="1">
+        <v>46245</v>
+      </c>
+      <c r="B69">
+        <v>1221</v>
+      </c>
+      <c r="C69">
+        <v>1122</v>
+      </c>
+      <c r="D69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B70">
+        <v>1221</v>
+      </c>
+      <c r="C70">
+        <v>1122</v>
+      </c>
+      <c r="D70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B71">
+        <v>1221</v>
+      </c>
+      <c r="C71">
+        <v>1122</v>
+      </c>
+      <c r="D71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B72">
+        <v>1221</v>
+      </c>
+      <c r="C72">
+        <v>1122</v>
+      </c>
+      <c r="D72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B73">
+        <v>1221</v>
+      </c>
+      <c r="C73">
+        <v>1122</v>
+      </c>
+      <c r="D73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B74">
+        <v>1221</v>
+      </c>
+      <c r="C74">
+        <v>1122</v>
+      </c>
+      <c r="D74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B75">
+        <v>1221</v>
+      </c>
+      <c r="C75">
+        <v>1122</v>
+      </c>
+      <c r="D75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A76" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B76">
+        <v>1221</v>
+      </c>
+      <c r="C76">
+        <v>1122</v>
+      </c>
+      <c r="D76">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B77">
+        <v>1221</v>
+      </c>
+      <c r="C77">
+        <v>1122</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B78">
+        <v>1221</v>
+      </c>
+      <c r="C78">
+        <v>1122</v>
+      </c>
+      <c r="D78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B79">
+        <v>1221</v>
+      </c>
+      <c r="C79">
+        <v>1122</v>
+      </c>
+      <c r="D79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B80">
+        <v>1221</v>
+      </c>
+      <c r="C80">
+        <v>1122</v>
+      </c>
+      <c r="D80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A81" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B81">
+        <v>1221</v>
+      </c>
+      <c r="C81">
+        <v>1122</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A82" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B82">
+        <v>1221</v>
+      </c>
+      <c r="C82">
+        <v>1122</v>
+      </c>
+      <c r="D82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B83">
+        <v>1221</v>
+      </c>
+      <c r="C83">
+        <v>1122</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B84">
+        <v>1221</v>
+      </c>
+      <c r="C84">
+        <v>1122</v>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B85">
+        <v>1221</v>
+      </c>
+      <c r="C85">
+        <v>1122</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B86">
+        <v>1221</v>
+      </c>
+      <c r="C86">
+        <v>1122</v>
+      </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B87">
+        <v>1221</v>
+      </c>
+      <c r="C87">
+        <v>1122</v>
+      </c>
+      <c r="D87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B88">
+        <v>1221</v>
+      </c>
+      <c r="C88">
+        <v>1122</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B89">
+        <v>1221</v>
+      </c>
+      <c r="C89">
+        <v>1122</v>
+      </c>
+      <c r="D89">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B90">
+        <v>1221</v>
+      </c>
+      <c r="C90">
+        <v>1122</v>
+      </c>
+      <c r="D90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B91">
+        <v>1221</v>
+      </c>
+      <c r="C91">
+        <v>1122</v>
+      </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B92">
+        <v>1221</v>
+      </c>
+      <c r="C92">
+        <v>1122</v>
+      </c>
+      <c r="D92">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B93">
+        <v>1221</v>
+      </c>
+      <c r="C93">
+        <v>1122</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B94">
+        <v>1221</v>
+      </c>
+      <c r="C94">
+        <v>1122</v>
+      </c>
+      <c r="D94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B95">
+        <v>1221</v>
+      </c>
+      <c r="C95">
+        <v>1122</v>
+      </c>
+      <c r="D95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A96" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B96">
+        <v>1221</v>
+      </c>
+      <c r="C96">
+        <v>1122</v>
+      </c>
+      <c r="D96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A97" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B97">
+        <v>1221</v>
+      </c>
+      <c r="C97">
+        <v>1122</v>
+      </c>
+      <c r="D97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A98" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B98">
+        <v>1221</v>
+      </c>
+      <c r="C98">
+        <v>1122</v>
+      </c>
+      <c r="D98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A99" s="1">
+        <v>46275</v>
+      </c>
+      <c r="B99">
+        <v>1221</v>
+      </c>
+      <c r="C99">
+        <v>1122</v>
+      </c>
+      <c r="D99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A100" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B100">
+        <v>1221</v>
+      </c>
+      <c r="C100">
+        <v>1122</v>
+      </c>
+      <c r="D100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A101" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B101">
+        <v>1221</v>
+      </c>
+      <c r="C101">
+        <v>1122</v>
+      </c>
+      <c r="D101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A102" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B102">
+        <v>1221</v>
+      </c>
+      <c r="C102">
+        <v>1122</v>
+      </c>
+      <c r="D102">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A103" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B103">
+        <v>1221</v>
+      </c>
+      <c r="C103">
+        <v>1122</v>
+      </c>
+      <c r="D103">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A104" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B104">
+        <v>1221</v>
+      </c>
+      <c r="C104">
+        <v>1122</v>
+      </c>
+      <c r="D104">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B105">
+        <v>1221</v>
+      </c>
+      <c r="C105">
+        <v>1122</v>
+      </c>
+      <c r="D105">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B106">
+        <v>1221</v>
+      </c>
+      <c r="C106">
+        <v>1122</v>
+      </c>
+      <c r="D106">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B107">
+        <v>1221</v>
+      </c>
+      <c r="C107">
+        <v>1122</v>
+      </c>
+      <c r="D107">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B108">
+        <v>1221</v>
+      </c>
+      <c r="C108">
+        <v>1122</v>
+      </c>
+      <c r="D108">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B109">
+        <v>1221</v>
+      </c>
+      <c r="C109">
+        <v>1122</v>
+      </c>
+      <c r="D109">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B110">
+        <v>1221</v>
+      </c>
+      <c r="C110">
+        <v>1122</v>
+      </c>
+      <c r="D110">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B111">
+        <v>1221</v>
+      </c>
+      <c r="C111">
+        <v>1122</v>
+      </c>
+      <c r="D111">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B112">
+        <v>1221</v>
+      </c>
+      <c r="C112">
+        <v>1122</v>
+      </c>
+      <c r="D112">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B113">
+        <v>1221</v>
+      </c>
+      <c r="C113">
+        <v>1122</v>
+      </c>
+      <c r="D113">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B114">
+        <v>1221</v>
+      </c>
+      <c r="C114">
+        <v>1122</v>
+      </c>
+      <c r="D114">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B115">
+        <v>1221</v>
+      </c>
+      <c r="C115">
+        <v>1122</v>
+      </c>
+      <c r="D115">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B116">
+        <v>1221</v>
+      </c>
+      <c r="C116">
+        <v>1122</v>
+      </c>
+      <c r="D116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B117">
+        <v>1221</v>
+      </c>
+      <c r="C117">
+        <v>1122</v>
+      </c>
+      <c r="D117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B118">
+        <v>1221</v>
+      </c>
+      <c r="C118">
+        <v>1122</v>
+      </c>
+      <c r="D118">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B119">
+        <v>1221</v>
+      </c>
+      <c r="C119">
+        <v>1122</v>
+      </c>
+      <c r="D119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B120">
+        <v>1221</v>
+      </c>
+      <c r="C120">
+        <v>1122</v>
+      </c>
+      <c r="D120">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A121" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B121">
+        <v>1221</v>
+      </c>
+      <c r="C121">
+        <v>1122</v>
+      </c>
+      <c r="D121">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A122" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B122">
+        <v>1221</v>
+      </c>
+      <c r="C122">
+        <v>1122</v>
+      </c>
+      <c r="D122">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A123" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B123">
+        <v>1221</v>
+      </c>
+      <c r="C123">
+        <v>1122</v>
+      </c>
+      <c r="D123">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A124" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B124">
+        <v>1221</v>
+      </c>
+      <c r="C124">
+        <v>1122</v>
+      </c>
+      <c r="D124">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A125" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B125">
+        <v>1221</v>
+      </c>
+      <c r="C125">
+        <v>1122</v>
+      </c>
+      <c r="D125">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A126" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B126">
+        <v>1221</v>
+      </c>
+      <c r="C126">
+        <v>1122</v>
+      </c>
+      <c r="D126">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A127" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B127">
+        <v>1221</v>
+      </c>
+      <c r="C127">
+        <v>1122</v>
+      </c>
+      <c r="D127">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A128" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B128">
+        <v>1221</v>
+      </c>
+      <c r="C128">
+        <v>1122</v>
+      </c>
+      <c r="D128">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A129" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B129">
+        <v>1221</v>
+      </c>
+      <c r="C129">
+        <v>1122</v>
+      </c>
+      <c r="D129">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B130">
+        <v>1221</v>
+      </c>
+      <c r="C130">
+        <v>1122</v>
+      </c>
+      <c r="D130">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A131" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B131">
+        <v>1221</v>
+      </c>
+      <c r="C131">
+        <v>1122</v>
+      </c>
+      <c r="D131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A132" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B132">
+        <v>1221</v>
+      </c>
+      <c r="C132">
+        <v>1122</v>
+      </c>
+      <c r="D132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B133">
+        <v>1221</v>
+      </c>
+      <c r="C133">
+        <v>1122</v>
+      </c>
+      <c r="D133">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A134" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B134">
+        <v>1221</v>
+      </c>
+      <c r="C134">
+        <v>1122</v>
+      </c>
+      <c r="D134">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B135">
+        <v>1221</v>
+      </c>
+      <c r="C135">
+        <v>1122</v>
+      </c>
+      <c r="D135">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A136" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B136">
+        <v>1221</v>
+      </c>
+      <c r="C136">
+        <v>1122</v>
+      </c>
+      <c r="D136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A137" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B137">
+        <v>1221</v>
+      </c>
+      <c r="C137">
+        <v>1122</v>
+      </c>
+      <c r="D137">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A138" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B138">
+        <v>1221</v>
+      </c>
+      <c r="C138">
+        <v>1122</v>
+      </c>
+      <c r="D138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A139" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B139">
+        <v>1221</v>
+      </c>
+      <c r="C139">
+        <v>1122</v>
+      </c>
+      <c r="D139">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A140" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B140">
+        <v>1221</v>
+      </c>
+      <c r="C140">
+        <v>1122</v>
+      </c>
+      <c r="D140">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A141" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B141">
+        <v>1221</v>
+      </c>
+      <c r="C141">
+        <v>1122</v>
+      </c>
+      <c r="D141">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A142" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B142">
+        <v>1221</v>
+      </c>
+      <c r="C142">
+        <v>1122</v>
+      </c>
+      <c r="D142">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A143" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B143">
+        <v>1221</v>
+      </c>
+      <c r="C143">
+        <v>1122</v>
+      </c>
+      <c r="D143">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A144" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B144">
+        <v>1221</v>
+      </c>
+      <c r="C144">
+        <v>1122</v>
+      </c>
+      <c r="D144">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A145" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B145">
+        <v>1221</v>
+      </c>
+      <c r="C145">
+        <v>1122</v>
+      </c>
+      <c r="D145">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A146" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B146">
+        <v>1221</v>
+      </c>
+      <c r="C146">
+        <v>1122</v>
+      </c>
+      <c r="D146">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A147" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B147">
+        <v>1221</v>
+      </c>
+      <c r="C147">
+        <v>1122</v>
+      </c>
+      <c r="D147">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A148" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B148">
+        <v>1221</v>
+      </c>
+      <c r="C148">
+        <v>1122</v>
+      </c>
+      <c r="D148">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A149" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B149">
+        <v>1221</v>
+      </c>
+      <c r="C149">
+        <v>1122</v>
+      </c>
+      <c r="D149">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A150" s="1">
+        <v>46326</v>
+      </c>
+      <c r="B150">
+        <v>1221</v>
+      </c>
+      <c r="C150">
+        <v>1122</v>
+      </c>
+      <c r="D150">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A151" s="1">
+        <v>46327</v>
+      </c>
+      <c r="B151">
+        <v>1221</v>
+      </c>
+      <c r="C151">
+        <v>1122</v>
+      </c>
+      <c r="D151">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A152" s="1">
+        <v>46328</v>
+      </c>
+      <c r="B152">
+        <v>1221</v>
+      </c>
+      <c r="C152">
+        <v>1122</v>
+      </c>
+      <c r="D152">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A153" s="1">
+        <v>46329</v>
+      </c>
+      <c r="B153">
+        <v>1221</v>
+      </c>
+      <c r="C153">
+        <v>1122</v>
+      </c>
+      <c r="D153">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A154" s="1">
+        <v>46330</v>
+      </c>
+      <c r="B154">
+        <v>1221</v>
+      </c>
+      <c r="C154">
+        <v>1122</v>
+      </c>
+      <c r="D154">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A155" s="1">
+        <v>46331</v>
+      </c>
+      <c r="B155">
+        <v>1221</v>
+      </c>
+      <c r="C155">
+        <v>1122</v>
+      </c>
+      <c r="D155">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A156" s="1">
+        <v>46332</v>
+      </c>
+      <c r="B156">
+        <v>1221</v>
+      </c>
+      <c r="C156">
+        <v>1122</v>
+      </c>
+      <c r="D156">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A157" s="1">
+        <v>46333</v>
+      </c>
+      <c r="B157">
+        <v>1221</v>
+      </c>
+      <c r="C157">
+        <v>1122</v>
+      </c>
+      <c r="D157">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A158" s="1">
+        <v>46334</v>
+      </c>
+      <c r="B158">
+        <v>1221</v>
+      </c>
+      <c r="C158">
+        <v>1122</v>
+      </c>
+      <c r="D158">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A159" s="1">
+        <v>46335</v>
+      </c>
+      <c r="B159">
+        <v>1221</v>
+      </c>
+      <c r="C159">
+        <v>1122</v>
+      </c>
+      <c r="D159">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A160" s="1">
+        <v>46336</v>
+      </c>
+      <c r="B160">
+        <v>1221</v>
+      </c>
+      <c r="C160">
+        <v>1122</v>
+      </c>
+      <c r="D160">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A161" s="1">
+        <v>46337</v>
+      </c>
+      <c r="B161">
+        <v>1221</v>
+      </c>
+      <c r="C161">
+        <v>1122</v>
+      </c>
+      <c r="D161">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A162" s="1">
+        <v>46338</v>
+      </c>
+      <c r="B162">
+        <v>1221</v>
+      </c>
+      <c r="C162">
+        <v>1122</v>
+      </c>
+      <c r="D162">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A163" s="1">
+        <v>46339</v>
+      </c>
+      <c r="B163">
+        <v>1221</v>
+      </c>
+      <c r="C163">
+        <v>1122</v>
+      </c>
+      <c r="D163">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A164" s="1">
+        <v>46340</v>
+      </c>
+      <c r="B164">
+        <v>1221</v>
+      </c>
+      <c r="C164">
+        <v>1122</v>
+      </c>
+      <c r="D164">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A165" s="1">
+        <v>46341</v>
+      </c>
+      <c r="B165">
+        <v>1221</v>
+      </c>
+      <c r="C165">
+        <v>1122</v>
+      </c>
+      <c r="D165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A166" s="1">
+        <v>46342</v>
+      </c>
+      <c r="B166">
+        <v>1221</v>
+      </c>
+      <c r="C166">
+        <v>1122</v>
+      </c>
+      <c r="D166">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A167" s="1">
+        <v>46343</v>
+      </c>
+      <c r="B167">
+        <v>1221</v>
+      </c>
+      <c r="C167">
+        <v>1122</v>
+      </c>
+      <c r="D167">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A168" s="1">
+        <v>46344</v>
+      </c>
+      <c r="B168">
+        <v>1221</v>
+      </c>
+      <c r="C168">
+        <v>1122</v>
+      </c>
+      <c r="D168">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A169" s="1">
+        <v>46345</v>
+      </c>
+      <c r="B169">
+        <v>1221</v>
+      </c>
+      <c r="C169">
+        <v>1122</v>
+      </c>
+      <c r="D169">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A170" s="1">
+        <v>46346</v>
+      </c>
+      <c r="B170">
+        <v>1221</v>
+      </c>
+      <c r="C170">
+        <v>1122</v>
+      </c>
+      <c r="D170">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A171" s="1">
+        <v>46347</v>
+      </c>
+      <c r="B171">
+        <v>1221</v>
+      </c>
+      <c r="C171">
+        <v>1122</v>
+      </c>
+      <c r="D171">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A172" s="1">
+        <v>46348</v>
+      </c>
+      <c r="B172">
+        <v>1221</v>
+      </c>
+      <c r="C172">
+        <v>1122</v>
+      </c>
+      <c r="D172">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A173" s="1">
+        <v>46349</v>
+      </c>
+      <c r="B173">
+        <v>1221</v>
+      </c>
+      <c r="C173">
+        <v>1122</v>
+      </c>
+      <c r="D173">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A174" s="1">
+        <v>46350</v>
+      </c>
+      <c r="B174">
+        <v>1221</v>
+      </c>
+      <c r="C174">
+        <v>1122</v>
+      </c>
+      <c r="D174">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A175" s="1">
+        <v>46351</v>
+      </c>
+      <c r="B175">
+        <v>1221</v>
+      </c>
+      <c r="C175">
+        <v>1122</v>
+      </c>
+      <c r="D175">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A176" s="1">
+        <v>46352</v>
+      </c>
+      <c r="B176">
+        <v>1221</v>
+      </c>
+      <c r="C176">
+        <v>1122</v>
+      </c>
+      <c r="D176">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A177" s="1">
+        <v>46353</v>
+      </c>
+      <c r="B177">
+        <v>1221</v>
+      </c>
+      <c r="C177">
+        <v>1122</v>
+      </c>
+      <c r="D177">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A178" s="1">
+        <v>46354</v>
+      </c>
+      <c r="B178">
+        <v>1221</v>
+      </c>
+      <c r="C178">
+        <v>1122</v>
+      </c>
+      <c r="D178">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A179" s="1">
+        <v>46355</v>
+      </c>
+      <c r="B179">
+        <v>1221</v>
+      </c>
+      <c r="C179">
+        <v>1122</v>
+      </c>
+      <c r="D179">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A180" s="1">
+        <v>46356</v>
+      </c>
+      <c r="B180">
+        <v>1221</v>
+      </c>
+      <c r="C180">
+        <v>1122</v>
+      </c>
+      <c r="D180">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A181" s="1">
+        <v>46357</v>
+      </c>
+      <c r="B181">
+        <v>1221</v>
+      </c>
+      <c r="C181">
+        <v>1122</v>
+      </c>
+      <c r="D181">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A182" s="1">
+        <v>46358</v>
+      </c>
+      <c r="B182">
+        <v>1221</v>
+      </c>
+      <c r="C182">
+        <v>1122</v>
+      </c>
+      <c r="D182">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A183" s="1">
+        <v>46359</v>
+      </c>
+      <c r="B183">
+        <v>1221</v>
+      </c>
+      <c r="C183">
+        <v>1122</v>
+      </c>
+      <c r="D183">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A184" s="1">
+        <v>46360</v>
+      </c>
+      <c r="B184">
+        <v>1221</v>
+      </c>
+      <c r="C184">
+        <v>1122</v>
+      </c>
+      <c r="D184">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A185" s="1">
+        <v>46361</v>
+      </c>
+      <c r="B185">
+        <v>1221</v>
+      </c>
+      <c r="C185">
+        <v>1122</v>
+      </c>
+      <c r="D185">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A186" s="1">
+        <v>46362</v>
+      </c>
+      <c r="B186">
+        <v>1221</v>
+      </c>
+      <c r="C186">
+        <v>1122</v>
+      </c>
+      <c r="D186">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A187" s="1">
+        <v>46363</v>
+      </c>
+      <c r="B187">
+        <v>1221</v>
+      </c>
+      <c r="C187">
+        <v>1122</v>
+      </c>
+      <c r="D187">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A188" s="1">
+        <v>46364</v>
+      </c>
+      <c r="B188">
+        <v>1221</v>
+      </c>
+      <c r="C188">
+        <v>1122</v>
+      </c>
+      <c r="D188">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A189" s="1">
+        <v>46365</v>
+      </c>
+      <c r="B189">
+        <v>1221</v>
+      </c>
+      <c r="C189">
+        <v>1122</v>
+      </c>
+      <c r="D189">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A190" s="1">
+        <v>46366</v>
+      </c>
+      <c r="B190">
+        <v>1221</v>
+      </c>
+      <c r="C190">
+        <v>1122</v>
+      </c>
+      <c r="D190">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A191" s="1">
+        <v>46367</v>
+      </c>
+      <c r="B191">
+        <v>1221</v>
+      </c>
+      <c r="C191">
+        <v>1122</v>
+      </c>
+      <c r="D191">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A192" s="1">
+        <v>46368</v>
+      </c>
+      <c r="B192">
+        <v>1221</v>
+      </c>
+      <c r="C192">
+        <v>1122</v>
+      </c>
+      <c r="D192">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A193" s="1">
+        <v>46369</v>
+      </c>
+      <c r="B193">
+        <v>1221</v>
+      </c>
+      <c r="C193">
+        <v>1122</v>
+      </c>
+      <c r="D193">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A194" s="1">
+        <v>46370</v>
+      </c>
+      <c r="B194">
+        <v>1221</v>
+      </c>
+      <c r="C194">
+        <v>1122</v>
+      </c>
+      <c r="D194">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A195" s="1">
+        <v>46371</v>
+      </c>
+      <c r="B195">
+        <v>1221</v>
+      </c>
+      <c r="C195">
+        <v>1122</v>
+      </c>
+      <c r="D195">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A196" s="1">
+        <v>46372</v>
+      </c>
+      <c r="B196">
+        <v>1221</v>
+      </c>
+      <c r="C196">
+        <v>1122</v>
+      </c>
+      <c r="D196">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A197" s="1">
+        <v>46373</v>
+      </c>
+      <c r="B197">
+        <v>1221</v>
+      </c>
+      <c r="C197">
+        <v>1122</v>
+      </c>
+      <c r="D197">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A198" s="1">
+        <v>46374</v>
+      </c>
+      <c r="B198">
+        <v>1221</v>
+      </c>
+      <c r="C198">
+        <v>1122</v>
+      </c>
+      <c r="D198">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A199" s="1">
+        <v>46375</v>
+      </c>
+      <c r="B199">
+        <v>1221</v>
+      </c>
+      <c r="C199">
+        <v>1122</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A200" s="1">
+        <v>46376</v>
+      </c>
+      <c r="B200">
+        <v>1221</v>
+      </c>
+      <c r="C200">
+        <v>1122</v>
+      </c>
+      <c r="D200">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A201" s="1">
+        <v>46377</v>
+      </c>
+      <c r="B201">
+        <v>1221</v>
+      </c>
+      <c r="C201">
+        <v>1122</v>
+      </c>
+      <c r="D201">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A202" s="1">
+        <v>46378</v>
+      </c>
+      <c r="B202">
+        <v>1221</v>
+      </c>
+      <c r="C202">
+        <v>1122</v>
+      </c>
+      <c r="D202">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A203" s="1">
+        <v>46379</v>
+      </c>
+      <c r="B203">
+        <v>1221</v>
+      </c>
+      <c r="C203">
+        <v>1122</v>
+      </c>
+      <c r="D203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A204" s="1">
+        <v>46380</v>
+      </c>
+      <c r="B204">
+        <v>1221</v>
+      </c>
+      <c r="C204">
+        <v>1122</v>
+      </c>
+      <c r="D204">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A205" s="1">
+        <v>46381</v>
+      </c>
+      <c r="B205">
+        <v>1221</v>
+      </c>
+      <c r="C205">
+        <v>1122</v>
+      </c>
+      <c r="D205">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A206" s="1">
+        <v>46382</v>
+      </c>
+      <c r="B206">
+        <v>1221</v>
+      </c>
+      <c r="C206">
+        <v>1122</v>
+      </c>
+      <c r="D206">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A207" s="1">
+        <v>46383</v>
+      </c>
+      <c r="B207">
+        <v>1221</v>
+      </c>
+      <c r="C207">
+        <v>1122</v>
+      </c>
+      <c r="D207">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A208" s="1">
+        <v>46384</v>
+      </c>
+      <c r="B208">
+        <v>1221</v>
+      </c>
+      <c r="C208">
+        <v>1122</v>
+      </c>
+      <c r="D208">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A209" s="1">
+        <v>46385</v>
+      </c>
+      <c r="B209">
+        <v>1221</v>
+      </c>
+      <c r="C209">
+        <v>1122</v>
+      </c>
+      <c r="D209">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A210" s="1">
+        <v>46386</v>
+      </c>
+      <c r="B210">
+        <v>1221</v>
+      </c>
+      <c r="C210">
+        <v>1122</v>
+      </c>
+      <c r="D210">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A211" s="1">
+        <v>46387</v>
+      </c>
+      <c r="B211">
+        <v>1221</v>
+      </c>
+      <c r="C211">
+        <v>1122</v>
+      </c>
+      <c r="D211">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A212" s="1">
+        <v>46388</v>
+      </c>
+      <c r="B212">
+        <v>1221</v>
+      </c>
+      <c r="C212">
+        <v>1122</v>
+      </c>
+      <c r="D212">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A213" s="1">
+        <v>46389</v>
+      </c>
+      <c r="B213">
+        <v>1221</v>
+      </c>
+      <c r="C213">
+        <v>1122</v>
+      </c>
+      <c r="D213">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A214" s="1">
+        <v>46390</v>
+      </c>
+      <c r="B214">
+        <v>1221</v>
+      </c>
+      <c r="C214">
+        <v>1122</v>
+      </c>
+      <c r="D214">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A215" s="1">
+        <v>46391</v>
+      </c>
+      <c r="B215">
+        <v>1221</v>
+      </c>
+      <c r="C215">
+        <v>1122</v>
+      </c>
+      <c r="D215">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A216" s="1">
+        <v>46392</v>
+      </c>
+      <c r="B216">
+        <v>1221</v>
+      </c>
+      <c r="C216">
+        <v>1122</v>
+      </c>
+      <c r="D216">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A217" s="1">
+        <v>46393</v>
+      </c>
+      <c r="B217">
+        <v>1221</v>
+      </c>
+      <c r="C217">
+        <v>1122</v>
+      </c>
+      <c r="D217">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A218" s="1">
+        <v>46394</v>
+      </c>
+      <c r="B218">
+        <v>1221</v>
+      </c>
+      <c r="C218">
+        <v>1122</v>
+      </c>
+      <c r="D218">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A219" s="1">
+        <v>46395</v>
+      </c>
+      <c r="B219">
+        <v>1221</v>
+      </c>
+      <c r="C219">
+        <v>1122</v>
+      </c>
+      <c r="D219">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A220" s="1">
+        <v>46396</v>
+      </c>
+      <c r="B220">
+        <v>1221</v>
+      </c>
+      <c r="C220">
+        <v>1122</v>
+      </c>
+      <c r="D220">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A221" s="1">
+        <v>46397</v>
+      </c>
+      <c r="B221">
+        <v>1221</v>
+      </c>
+      <c r="C221">
+        <v>1122</v>
+      </c>
+      <c r="D221">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A222" s="1">
+        <v>46398</v>
+      </c>
+      <c r="B222">
+        <v>1221</v>
+      </c>
+      <c r="C222">
+        <v>1122</v>
+      </c>
+      <c r="D222">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A223" s="1">
+        <v>46399</v>
+      </c>
+      <c r="B223">
+        <v>1221</v>
+      </c>
+      <c r="C223">
+        <v>1122</v>
+      </c>
+      <c r="D223">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A224" s="1">
+        <v>46400</v>
+      </c>
+      <c r="B224">
+        <v>1221</v>
+      </c>
+      <c r="C224">
+        <v>1122</v>
+      </c>
+      <c r="D224">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A225" s="1">
+        <v>46401</v>
+      </c>
+      <c r="B225">
+        <v>1221</v>
+      </c>
+      <c r="C225">
+        <v>1122</v>
+      </c>
+      <c r="D225">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A226" s="1">
+        <v>46402</v>
+      </c>
+      <c r="B226">
+        <v>1221</v>
+      </c>
+      <c r="C226">
+        <v>1122</v>
+      </c>
+      <c r="D226">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A227" s="1">
+        <v>46403</v>
+      </c>
+      <c r="B227">
+        <v>1221</v>
+      </c>
+      <c r="C227">
+        <v>1122</v>
+      </c>
+      <c r="D227">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A228" s="1">
+        <v>46404</v>
+      </c>
+      <c r="B228">
+        <v>1221</v>
+      </c>
+      <c r="C228">
+        <v>1122</v>
+      </c>
+      <c r="D228">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A229" s="1">
+        <v>46405</v>
+      </c>
+      <c r="B229">
+        <v>1221</v>
+      </c>
+      <c r="C229">
+        <v>1122</v>
+      </c>
+      <c r="D229">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A230" s="1">
+        <v>46406</v>
+      </c>
+      <c r="B230">
+        <v>1221</v>
+      </c>
+      <c r="C230">
+        <v>1122</v>
+      </c>
+      <c r="D230">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A231" s="1">
+        <v>46407</v>
+      </c>
+      <c r="B231">
+        <v>1221</v>
+      </c>
+      <c r="C231">
+        <v>1122</v>
+      </c>
+      <c r="D231">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A232" s="1">
+        <v>46408</v>
+      </c>
+      <c r="B232">
+        <v>1221</v>
+      </c>
+      <c r="C232">
+        <v>1122</v>
+      </c>
+      <c r="D232">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A233" s="1">
+        <v>46409</v>
+      </c>
+      <c r="B233">
+        <v>1221</v>
+      </c>
+      <c r="C233">
+        <v>1122</v>
+      </c>
+      <c r="D233">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A234" s="1">
+        <v>46410</v>
+      </c>
+      <c r="B234">
+        <v>1221</v>
+      </c>
+      <c r="C234">
+        <v>1122</v>
+      </c>
+      <c r="D234">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A235" s="1">
+        <v>46411</v>
+      </c>
+      <c r="B235">
+        <v>1221</v>
+      </c>
+      <c r="C235">
+        <v>1122</v>
+      </c>
+      <c r="D235">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A236" s="1">
+        <v>46412</v>
+      </c>
+      <c r="B236">
+        <v>1221</v>
+      </c>
+      <c r="C236">
+        <v>1122</v>
+      </c>
+      <c r="D236">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A237" s="1">
+        <v>46413</v>
+      </c>
+      <c r="B237">
+        <v>1221</v>
+      </c>
+      <c r="C237">
+        <v>1122</v>
+      </c>
+      <c r="D237">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A238" s="1">
+        <v>46414</v>
+      </c>
+      <c r="B238">
+        <v>1221</v>
+      </c>
+      <c r="C238">
+        <v>1122</v>
+      </c>
+      <c r="D238">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A239" s="1">
+        <v>46415</v>
+      </c>
+      <c r="B239">
+        <v>1221</v>
+      </c>
+      <c r="C239">
+        <v>1122</v>
+      </c>
+      <c r="D239">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A240" s="1">
+        <v>46416</v>
+      </c>
+      <c r="B240">
+        <v>1221</v>
+      </c>
+      <c r="C240">
+        <v>1122</v>
+      </c>
+      <c r="D240">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A241" s="1">
+        <v>46417</v>
+      </c>
+      <c r="B241">
+        <v>1221</v>
+      </c>
+      <c r="C241">
+        <v>1122</v>
+      </c>
+      <c r="D241">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A242" s="1">
+        <v>46418</v>
+      </c>
+      <c r="B242">
+        <v>1221</v>
+      </c>
+      <c r="C242">
+        <v>1122</v>
+      </c>
+      <c r="D242">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A243" s="1">
+        <v>46419</v>
+      </c>
+      <c r="B243">
+        <v>1221</v>
+      </c>
+      <c r="C243">
+        <v>1122</v>
+      </c>
+      <c r="D243">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A244" s="1">
+        <v>46420</v>
+      </c>
+      <c r="B244">
+        <v>1221</v>
+      </c>
+      <c r="C244">
+        <v>1122</v>
+      </c>
+      <c r="D244">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A245" s="1">
+        <v>46421</v>
+      </c>
+      <c r="B245">
+        <v>1221</v>
+      </c>
+      <c r="C245">
+        <v>1122</v>
+      </c>
+      <c r="D245">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A246" s="1">
+        <v>46422</v>
+      </c>
+      <c r="B246">
+        <v>1221</v>
+      </c>
+      <c r="C246">
+        <v>1122</v>
+      </c>
+      <c r="D246">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A247" s="1">
+        <v>46423</v>
+      </c>
+      <c r="B247">
+        <v>1221</v>
+      </c>
+      <c r="C247">
+        <v>1122</v>
+      </c>
+      <c r="D247">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A248" s="1">
+        <v>46424</v>
+      </c>
+      <c r="B248">
+        <v>1221</v>
+      </c>
+      <c r="C248">
+        <v>1122</v>
+      </c>
+      <c r="D248">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A249" s="1">
+        <v>46425</v>
+      </c>
+      <c r="B249">
+        <v>1221</v>
+      </c>
+      <c r="C249">
+        <v>1122</v>
+      </c>
+      <c r="D249">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A250" s="1">
+        <v>46426</v>
+      </c>
+      <c r="B250">
+        <v>1221</v>
+      </c>
+      <c r="C250">
+        <v>1122</v>
+      </c>
+      <c r="D250">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A251" s="1">
+        <v>46427</v>
+      </c>
+      <c r="B251">
+        <v>1221</v>
+      </c>
+      <c r="C251">
+        <v>1122</v>
+      </c>
+      <c r="D251">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A252" s="1">
+        <v>46428</v>
+      </c>
+      <c r="B252">
+        <v>1221</v>
+      </c>
+      <c r="C252">
+        <v>1122</v>
+      </c>
+      <c r="D252">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A253" s="1">
+        <v>46429</v>
+      </c>
+      <c r="B253">
+        <v>1221</v>
+      </c>
+      <c r="C253">
+        <v>1122</v>
+      </c>
+      <c r="D253">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A254" s="1">
+        <v>46430</v>
+      </c>
+      <c r="B254">
+        <v>1221</v>
+      </c>
+      <c r="C254">
+        <v>1122</v>
+      </c>
+      <c r="D254">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A255" s="1">
+        <v>46431</v>
+      </c>
+      <c r="B255">
+        <v>1221</v>
+      </c>
+      <c r="C255">
+        <v>1122</v>
+      </c>
+      <c r="D255">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A256" s="1">
+        <v>46432</v>
+      </c>
+      <c r="B256">
+        <v>1221</v>
+      </c>
+      <c r="C256">
+        <v>1122</v>
+      </c>
+      <c r="D256">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A257" s="1">
+        <v>46433</v>
+      </c>
+      <c r="B257">
+        <v>1221</v>
+      </c>
+      <c r="C257">
+        <v>1122</v>
+      </c>
+      <c r="D257">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A258" s="1">
+        <v>46434</v>
+      </c>
+      <c r="B258">
+        <v>1221</v>
+      </c>
+      <c r="C258">
+        <v>1122</v>
+      </c>
+      <c r="D258">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A259" s="1">
+        <v>46435</v>
+      </c>
+      <c r="B259">
+        <v>1221</v>
+      </c>
+      <c r="C259">
+        <v>1122</v>
+      </c>
+      <c r="D259">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A260" s="1">
+        <v>46436</v>
+      </c>
+      <c r="B260">
+        <v>1221</v>
+      </c>
+      <c r="C260">
+        <v>1122</v>
+      </c>
+      <c r="D260">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A261" s="1">
+        <v>46437</v>
+      </c>
+      <c r="B261">
+        <v>1221</v>
+      </c>
+      <c r="C261">
+        <v>1122</v>
+      </c>
+      <c r="D261">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A262" s="1">
+        <v>46438</v>
+      </c>
+      <c r="B262">
+        <v>1221</v>
+      </c>
+      <c r="C262">
+        <v>1122</v>
+      </c>
+      <c r="D262">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A263" s="1">
+        <v>46439</v>
+      </c>
+      <c r="B263">
+        <v>1221</v>
+      </c>
+      <c r="C263">
+        <v>1122</v>
+      </c>
+      <c r="D263">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A264" s="1">
+        <v>46440</v>
+      </c>
+      <c r="B264">
+        <v>1221</v>
+      </c>
+      <c r="C264">
+        <v>1122</v>
+      </c>
+      <c r="D264">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A265" s="1">
+        <v>46441</v>
+      </c>
+      <c r="B265">
+        <v>1221</v>
+      </c>
+      <c r="C265">
+        <v>1122</v>
+      </c>
+      <c r="D265">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A266" s="1">
+        <v>46442</v>
+      </c>
+      <c r="B266">
+        <v>1221</v>
+      </c>
+      <c r="C266">
+        <v>1122</v>
+      </c>
+      <c r="D266">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A267" s="1">
+        <v>46443</v>
+      </c>
+      <c r="B267">
+        <v>1221</v>
+      </c>
+      <c r="C267">
+        <v>1122</v>
+      </c>
+      <c r="D267">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A268" s="1">
+        <v>46444</v>
+      </c>
+      <c r="B268">
+        <v>1221</v>
+      </c>
+      <c r="C268">
+        <v>1122</v>
+      </c>
+      <c r="D268">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A269" s="1">
+        <v>46445</v>
+      </c>
+      <c r="B269">
+        <v>1221</v>
+      </c>
+      <c r="C269">
+        <v>1122</v>
+      </c>
+      <c r="D269">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A270" s="1">
+        <v>46446</v>
+      </c>
+      <c r="B270">
+        <v>1221</v>
+      </c>
+      <c r="C270">
+        <v>1122</v>
+      </c>
+      <c r="D270">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A271" s="1">
+        <v>46447</v>
+      </c>
+      <c r="B271">
+        <v>1221</v>
+      </c>
+      <c r="C271">
+        <v>1122</v>
+      </c>
+      <c r="D271">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A272" s="1">
+        <v>46448</v>
+      </c>
+      <c r="B272">
+        <v>1221</v>
+      </c>
+      <c r="C272">
+        <v>1122</v>
+      </c>
+      <c r="D272">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A273" s="1">
+        <v>46449</v>
+      </c>
+      <c r="B273">
+        <v>1221</v>
+      </c>
+      <c r="C273">
+        <v>1122</v>
+      </c>
+      <c r="D273">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A274" s="1">
+        <v>46450</v>
+      </c>
+      <c r="B274">
+        <v>1221</v>
+      </c>
+      <c r="C274">
+        <v>1122</v>
+      </c>
+      <c r="D274">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A275" s="1">
+        <v>46451</v>
+      </c>
+      <c r="B275">
+        <v>1221</v>
+      </c>
+      <c r="C275">
+        <v>1122</v>
+      </c>
+      <c r="D275">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A276" s="1">
+        <v>46452</v>
+      </c>
+      <c r="B276">
+        <v>1221</v>
+      </c>
+      <c r="C276">
+        <v>1122</v>
+      </c>
+      <c r="D276">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A277" s="1">
+        <v>46453</v>
+      </c>
+      <c r="B277">
+        <v>1221</v>
+      </c>
+      <c r="C277">
+        <v>1122</v>
+      </c>
+      <c r="D277">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A278" s="1">
+        <v>46454</v>
+      </c>
+      <c r="B278">
+        <v>1221</v>
+      </c>
+      <c r="C278">
+        <v>1122</v>
+      </c>
+      <c r="D278">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A279" s="1">
+        <v>46455</v>
+      </c>
+      <c r="B279">
+        <v>1221</v>
+      </c>
+      <c r="C279">
+        <v>1122</v>
+      </c>
+      <c r="D279">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A280" s="1">
+        <v>46456</v>
+      </c>
+      <c r="B280">
+        <v>1221</v>
+      </c>
+      <c r="C280">
+        <v>1122</v>
+      </c>
+      <c r="D280">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A281" s="1">
+        <v>46457</v>
+      </c>
+      <c r="B281">
+        <v>1221</v>
+      </c>
+      <c r="C281">
+        <v>1122</v>
+      </c>
+      <c r="D281">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A282" s="1">
+        <v>46458</v>
+      </c>
+      <c r="B282">
+        <v>1221</v>
+      </c>
+      <c r="C282">
+        <v>1122</v>
+      </c>
+      <c r="D282">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A283" s="1">
+        <v>46459</v>
+      </c>
+      <c r="B283">
+        <v>1221</v>
+      </c>
+      <c r="C283">
+        <v>1122</v>
+      </c>
+      <c r="D283">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A284" s="1">
+        <v>46460</v>
+      </c>
+      <c r="B284">
+        <v>1221</v>
+      </c>
+      <c r="C284">
+        <v>1122</v>
+      </c>
+      <c r="D284">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A285" s="1">
+        <v>46461</v>
+      </c>
+      <c r="B285">
+        <v>1221</v>
+      </c>
+      <c r="C285">
+        <v>1122</v>
+      </c>
+      <c r="D285">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A286" s="1">
+        <v>46462</v>
+      </c>
+      <c r="B286">
+        <v>1221</v>
+      </c>
+      <c r="C286">
+        <v>1122</v>
+      </c>
+      <c r="D286">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A287" s="1">
+        <v>46463</v>
+      </c>
+      <c r="B287">
+        <v>1221</v>
+      </c>
+      <c r="C287">
+        <v>1122</v>
+      </c>
+      <c r="D287">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A288" s="1">
+        <v>46464</v>
+      </c>
+      <c r="B288">
+        <v>1221</v>
+      </c>
+      <c r="C288">
+        <v>1122</v>
+      </c>
+      <c r="D288">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A289" s="1">
+        <v>46465</v>
+      </c>
+      <c r="B289">
+        <v>1221</v>
+      </c>
+      <c r="C289">
+        <v>1122</v>
+      </c>
+      <c r="D289">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A290" s="1">
+        <v>46466</v>
+      </c>
+      <c r="B290">
+        <v>1221</v>
+      </c>
+      <c r="C290">
+        <v>1122</v>
+      </c>
+      <c r="D290">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A291" s="1">
+        <v>46467</v>
+      </c>
+      <c r="B291">
+        <v>1221</v>
+      </c>
+      <c r="C291">
+        <v>1122</v>
+      </c>
+      <c r="D291">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A292" s="1">
+        <v>46468</v>
+      </c>
+      <c r="B292">
+        <v>1221</v>
+      </c>
+      <c r="C292">
+        <v>1122</v>
+      </c>
+      <c r="D292">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A293" s="1">
+        <v>46469</v>
+      </c>
+      <c r="B293">
+        <v>1221</v>
+      </c>
+      <c r="C293">
+        <v>1122</v>
+      </c>
+      <c r="D293">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A294" s="1">
+        <v>46470</v>
+      </c>
+      <c r="B294">
+        <v>1221</v>
+      </c>
+      <c r="C294">
+        <v>1122</v>
+      </c>
+      <c r="D294">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A295" s="1">
+        <v>46471</v>
+      </c>
+      <c r="B295">
+        <v>1221</v>
+      </c>
+      <c r="C295">
+        <v>1122</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A296" s="1">
+        <v>46472</v>
+      </c>
+      <c r="B296">
+        <v>1221</v>
+      </c>
+      <c r="C296">
+        <v>1122</v>
+      </c>
+      <c r="D296">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A297" s="1">
+        <v>46473</v>
+      </c>
+      <c r="B297">
+        <v>1221</v>
+      </c>
+      <c r="C297">
+        <v>1122</v>
+      </c>
+      <c r="D297">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A298" s="1">
+        <v>46474</v>
+      </c>
+      <c r="B298">
+        <v>1221</v>
+      </c>
+      <c r="C298">
+        <v>1122</v>
+      </c>
+      <c r="D298">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A299" s="1">
+        <v>46475</v>
+      </c>
+      <c r="B299">
+        <v>1221</v>
+      </c>
+      <c r="C299">
+        <v>1122</v>
+      </c>
+      <c r="D299">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A300" s="1">
+        <v>46476</v>
+      </c>
+      <c r="B300">
+        <v>1221</v>
+      </c>
+      <c r="C300">
+        <v>1122</v>
+      </c>
+      <c r="D300">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A301" s="1">
+        <v>46477</v>
+      </c>
+      <c r="B301">
+        <v>1221</v>
+      </c>
+      <c r="C301">
+        <v>1122</v>
+      </c>
+      <c r="D301">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A302" s="1">
+        <v>46478</v>
+      </c>
+      <c r="B302">
+        <v>1221</v>
+      </c>
+      <c r="C302">
+        <v>1122</v>
+      </c>
+      <c r="D302">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A303" s="1">
+        <v>46479</v>
+      </c>
+      <c r="B303">
+        <v>1221</v>
+      </c>
+      <c r="C303">
+        <v>1122</v>
+      </c>
+      <c r="D303">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A304" s="1">
+        <v>46480</v>
+      </c>
+      <c r="B304">
+        <v>1221</v>
+      </c>
+      <c r="C304">
+        <v>1122</v>
+      </c>
+      <c r="D304">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A305" s="1">
+        <v>46481</v>
+      </c>
+      <c r="B305">
+        <v>1221</v>
+      </c>
+      <c r="C305">
+        <v>1122</v>
+      </c>
+      <c r="D305">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A306" s="1">
+        <v>46482</v>
+      </c>
+      <c r="B306">
+        <v>1221</v>
+      </c>
+      <c r="C306">
+        <v>1122</v>
+      </c>
+      <c r="D306">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A307" s="1">
+        <v>46483</v>
+      </c>
+      <c r="B307">
+        <v>1221</v>
+      </c>
+      <c r="C307">
+        <v>1122</v>
+      </c>
+      <c r="D307">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A308" s="1">
+        <v>46484</v>
+      </c>
+      <c r="B308">
+        <v>1221</v>
+      </c>
+      <c r="C308">
+        <v>1122</v>
+      </c>
+      <c r="D308">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A309" s="1">
+        <v>46485</v>
+      </c>
+      <c r="B309">
+        <v>1221</v>
+      </c>
+      <c r="C309">
+        <v>1122</v>
+      </c>
+      <c r="D309">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A310" s="1">
+        <v>46486</v>
+      </c>
+      <c r="B310">
+        <v>1221</v>
+      </c>
+      <c r="C310">
+        <v>1122</v>
+      </c>
+      <c r="D310">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A311" s="1">
+        <v>46487</v>
+      </c>
+      <c r="B311">
+        <v>1221</v>
+      </c>
+      <c r="C311">
+        <v>1122</v>
+      </c>
+      <c r="D311">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A312" s="1">
+        <v>46488</v>
+      </c>
+      <c r="B312">
+        <v>1221</v>
+      </c>
+      <c r="C312">
+        <v>1122</v>
+      </c>
+      <c r="D312">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A313" s="1">
+        <v>46489</v>
+      </c>
+      <c r="B313">
+        <v>1221</v>
+      </c>
+      <c r="C313">
+        <v>1122</v>
+      </c>
+      <c r="D313">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A314" s="1">
+        <v>46490</v>
+      </c>
+      <c r="B314">
+        <v>1221</v>
+      </c>
+      <c r="C314">
+        <v>1122</v>
+      </c>
+      <c r="D314">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A315" s="1">
+        <v>46491</v>
+      </c>
+      <c r="B315">
+        <v>1221</v>
+      </c>
+      <c r="C315">
+        <v>1122</v>
+      </c>
+      <c r="D315">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A316" s="1">
+        <v>46492</v>
+      </c>
+      <c r="B316">
+        <v>1221</v>
+      </c>
+      <c r="C316">
+        <v>1122</v>
+      </c>
+      <c r="D316">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A317" s="1">
+        <v>46493</v>
+      </c>
+      <c r="B317">
+        <v>1221</v>
+      </c>
+      <c r="C317">
+        <v>1122</v>
+      </c>
+      <c r="D317">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A318" s="1">
+        <v>46494</v>
+      </c>
+      <c r="B318">
+        <v>1221</v>
+      </c>
+      <c r="C318">
+        <v>1122</v>
+      </c>
+      <c r="D318">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A319" s="1">
+        <v>46495</v>
+      </c>
+      <c r="B319">
+        <v>1221</v>
+      </c>
+      <c r="C319">
+        <v>1122</v>
+      </c>
+      <c r="D319">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A320" s="1">
+        <v>46496</v>
+      </c>
+      <c r="B320">
+        <v>1221</v>
+      </c>
+      <c r="C320">
+        <v>1122</v>
+      </c>
+      <c r="D320">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A321" s="1">
+        <v>46497</v>
+      </c>
+      <c r="B321">
+        <v>1221</v>
+      </c>
+      <c r="C321">
+        <v>1122</v>
+      </c>
+      <c r="D321">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A322" s="1">
+        <v>46498</v>
+      </c>
+      <c r="B322">
+        <v>1221</v>
+      </c>
+      <c r="C322">
+        <v>1122</v>
+      </c>
+      <c r="D322">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A323" s="1">
+        <v>46499</v>
+      </c>
+      <c r="B323">
+        <v>1221</v>
+      </c>
+      <c r="C323">
+        <v>1122</v>
+      </c>
+      <c r="D323">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A324" s="1">
+        <v>46500</v>
+      </c>
+      <c r="B324">
+        <v>1221</v>
+      </c>
+      <c r="C324">
+        <v>1122</v>
+      </c>
+      <c r="D324">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A325" s="1">
+        <v>46501</v>
+      </c>
+      <c r="B325">
+        <v>1221</v>
+      </c>
+      <c r="C325">
+        <v>1122</v>
+      </c>
+      <c r="D325">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A326" s="1">
+        <v>46502</v>
+      </c>
+      <c r="B326">
+        <v>1221</v>
+      </c>
+      <c r="C326">
+        <v>1122</v>
+      </c>
+      <c r="D326">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A327" s="1">
+        <v>46503</v>
+      </c>
+      <c r="B327">
+        <v>1221</v>
+      </c>
+      <c r="C327">
+        <v>1122</v>
+      </c>
+      <c r="D327">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A328" s="1">
+        <v>46504</v>
+      </c>
+      <c r="B328">
+        <v>1221</v>
+      </c>
+      <c r="C328">
+        <v>1122</v>
+      </c>
+      <c r="D328">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A329" s="1">
+        <v>46505</v>
+      </c>
+      <c r="B329">
+        <v>1221</v>
+      </c>
+      <c r="C329">
+        <v>1122</v>
+      </c>
+      <c r="D329">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A330" s="1">
+        <v>46506</v>
+      </c>
+      <c r="B330">
+        <v>1221</v>
+      </c>
+      <c r="C330">
+        <v>1122</v>
+      </c>
+      <c r="D330">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A331" s="1">
+        <v>46507</v>
+      </c>
+      <c r="B331">
+        <v>1221</v>
+      </c>
+      <c r="C331">
+        <v>1122</v>
+      </c>
+      <c r="D331">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A332" s="1">
+        <v>46508</v>
+      </c>
+      <c r="B332">
+        <v>1221</v>
+      </c>
+      <c r="C332">
+        <v>1122</v>
+      </c>
+      <c r="D332">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A333" s="1">
+        <v>46509</v>
+      </c>
+      <c r="B333">
+        <v>1221</v>
+      </c>
+      <c r="C333">
+        <v>1122</v>
+      </c>
+      <c r="D333">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A334" s="1">
+        <v>46510</v>
+      </c>
+      <c r="B334">
+        <v>1221</v>
+      </c>
+      <c r="C334">
+        <v>1122</v>
+      </c>
+      <c r="D334">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A335" s="1">
+        <v>46511</v>
+      </c>
+      <c r="B335">
+        <v>1221</v>
+      </c>
+      <c r="C335">
+        <v>1122</v>
+      </c>
+      <c r="D335">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A336" s="1">
+        <v>46512</v>
+      </c>
+      <c r="B336">
+        <v>1221</v>
+      </c>
+      <c r="C336">
+        <v>1122</v>
+      </c>
+      <c r="D336">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A337" s="1">
+        <v>46513</v>
+      </c>
+      <c r="B337">
+        <v>1221</v>
+      </c>
+      <c r="C337">
+        <v>1122</v>
+      </c>
+      <c r="D337">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A338" s="1">
+        <v>46514</v>
+      </c>
+      <c r="B338">
+        <v>1221</v>
+      </c>
+      <c r="C338">
+        <v>1122</v>
+      </c>
+      <c r="D338">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A339" s="1">
+        <v>46515</v>
+      </c>
+      <c r="B339">
+        <v>1221</v>
+      </c>
+      <c r="C339">
+        <v>1122</v>
+      </c>
+      <c r="D339">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A340" s="1">
+        <v>46516</v>
+      </c>
+      <c r="B340">
+        <v>1221</v>
+      </c>
+      <c r="C340">
+        <v>1122</v>
+      </c>
+      <c r="D340">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A341" s="1">
+        <v>46517</v>
+      </c>
+      <c r="B341">
+        <v>1221</v>
+      </c>
+      <c r="C341">
+        <v>1122</v>
+      </c>
+      <c r="D341">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A342" s="1">
+        <v>46518</v>
+      </c>
+      <c r="B342">
+        <v>1221</v>
+      </c>
+      <c r="C342">
+        <v>1122</v>
+      </c>
+      <c r="D342">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A343" s="1">
+        <v>46519</v>
+      </c>
+      <c r="B343">
+        <v>1221</v>
+      </c>
+      <c r="C343">
+        <v>1122</v>
+      </c>
+      <c r="D343">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A344" s="1">
+        <v>46520</v>
+      </c>
+      <c r="B344">
+        <v>1221</v>
+      </c>
+      <c r="C344">
+        <v>1122</v>
+      </c>
+      <c r="D344">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A345" s="1">
+        <v>46521</v>
+      </c>
+      <c r="B345">
+        <v>1221</v>
+      </c>
+      <c r="C345">
+        <v>1122</v>
+      </c>
+      <c r="D345">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A346" s="1">
+        <v>46522</v>
+      </c>
+      <c r="B346">
+        <v>1221</v>
+      </c>
+      <c r="C346">
+        <v>1122</v>
+      </c>
+      <c r="D346">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A347" s="1">
+        <v>46523</v>
+      </c>
+      <c r="B347">
+        <v>1221</v>
+      </c>
+      <c r="C347">
+        <v>1122</v>
+      </c>
+      <c r="D347">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A348" s="1">
+        <v>46524</v>
+      </c>
+      <c r="B348">
+        <v>1221</v>
+      </c>
+      <c r="C348">
+        <v>1122</v>
+      </c>
+      <c r="D348">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A349" s="1">
+        <v>46525</v>
+      </c>
+      <c r="B349">
+        <v>1221</v>
+      </c>
+      <c r="C349">
+        <v>1122</v>
+      </c>
+      <c r="D349">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A350" s="1">
+        <v>46526</v>
+      </c>
+      <c r="B350">
+        <v>1221</v>
+      </c>
+      <c r="C350">
+        <v>1122</v>
+      </c>
+      <c r="D350">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A351" s="1">
+        <v>46527</v>
+      </c>
+      <c r="B351">
+        <v>1221</v>
+      </c>
+      <c r="C351">
+        <v>1122</v>
+      </c>
+      <c r="D351">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A352" s="1">
+        <v>46528</v>
+      </c>
+      <c r="B352">
+        <v>1221</v>
+      </c>
+      <c r="C352">
+        <v>1122</v>
+      </c>
+      <c r="D352">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A353" s="1">
+        <v>46529</v>
+      </c>
+      <c r="B353">
+        <v>1221</v>
+      </c>
+      <c r="C353">
+        <v>1122</v>
+      </c>
+      <c r="D353">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A354" s="1">
+        <v>46530</v>
+      </c>
+      <c r="B354">
+        <v>1221</v>
+      </c>
+      <c r="C354">
+        <v>1122</v>
+      </c>
+      <c r="D354">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A355" s="1">
+        <v>46531</v>
+      </c>
+      <c r="B355">
+        <v>1221</v>
+      </c>
+      <c r="C355">
+        <v>1122</v>
+      </c>
+      <c r="D355">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A356" s="1">
+        <v>46532</v>
+      </c>
+      <c r="B356">
+        <v>1221</v>
+      </c>
+      <c r="C356">
+        <v>1122</v>
+      </c>
+      <c r="D356">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A357" s="1">
+        <v>46533</v>
+      </c>
+      <c r="B357">
+        <v>1221</v>
+      </c>
+      <c r="C357">
+        <v>1122</v>
+      </c>
+      <c r="D357">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A358" s="1">
+        <v>46534</v>
+      </c>
+      <c r="B358">
+        <v>1221</v>
+      </c>
+      <c r="C358">
+        <v>1122</v>
+      </c>
+      <c r="D358">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A359" s="1">
+        <v>46535</v>
+      </c>
+      <c r="B359">
+        <v>1221</v>
+      </c>
+      <c r="C359">
+        <v>1122</v>
+      </c>
+      <c r="D359">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A360" s="1">
+        <v>46536</v>
+      </c>
+      <c r="B360">
+        <v>1221</v>
+      </c>
+      <c r="C360">
+        <v>1122</v>
+      </c>
+      <c r="D360">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A361" s="1">
+        <v>46537</v>
+      </c>
+      <c r="B361">
+        <v>1221</v>
+      </c>
+      <c r="C361">
+        <v>1122</v>
+      </c>
+      <c r="D361">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A362" s="1">
+        <v>46538</v>
+      </c>
+      <c r="B362">
+        <v>1221</v>
+      </c>
+      <c r="C362">
+        <v>1122</v>
+      </c>
+      <c r="D362">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A363" s="1">
+        <v>46539</v>
+      </c>
+      <c r="B363">
+        <v>1221</v>
+      </c>
+      <c r="C363">
+        <v>1122</v>
+      </c>
+      <c r="D363">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A364" s="1">
+        <v>46540</v>
+      </c>
+      <c r="B364">
+        <v>1221</v>
+      </c>
+      <c r="C364">
+        <v>1122</v>
+      </c>
+      <c r="D364">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A365" s="1">
+        <v>46541</v>
+      </c>
+      <c r="B365">
+        <v>1221</v>
+      </c>
+      <c r="C365">
+        <v>1122</v>
+      </c>
+      <c r="D365">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A366" s="1">
+        <v>46542</v>
+      </c>
+      <c r="B366">
+        <v>1221</v>
+      </c>
+      <c r="C366">
+        <v>1122</v>
+      </c>
+      <c r="D366">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A367" s="1">
+        <v>46543</v>
+      </c>
+      <c r="B367">
+        <v>1221</v>
+      </c>
+      <c r="C367">
+        <v>1122</v>
+      </c>
+      <c r="D367">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A368" s="1">
+        <v>46544</v>
+      </c>
+      <c r="B368">
+        <v>1221</v>
+      </c>
+      <c r="C368">
+        <v>1122</v>
+      </c>
+      <c r="D368">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A369" s="1">
+        <v>46545</v>
+      </c>
+      <c r="B369">
+        <v>1221</v>
+      </c>
+      <c r="C369">
+        <v>1122</v>
+      </c>
+      <c r="D369">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A370" s="1">
+        <v>46546</v>
+      </c>
+      <c r="B370">
+        <v>1221</v>
+      </c>
+      <c r="C370">
+        <v>1122</v>
+      </c>
+      <c r="D370">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A371" s="1">
+        <v>46547</v>
+      </c>
+      <c r="B371">
+        <v>1221</v>
+      </c>
+      <c r="C371">
+        <v>1122</v>
+      </c>
+      <c r="D371">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A372" s="1">
+        <v>46548</v>
+      </c>
+      <c r="B372">
+        <v>1221</v>
+      </c>
+      <c r="C372">
+        <v>1122</v>
+      </c>
+      <c r="D372">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A373" s="1">
+        <v>46549</v>
+      </c>
+      <c r="B373">
+        <v>1221</v>
+      </c>
+      <c r="C373">
+        <v>1122</v>
+      </c>
+      <c r="D373">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A374" s="1">
+        <v>46550</v>
+      </c>
+      <c r="B374">
+        <v>1221</v>
+      </c>
+      <c r="C374">
+        <v>1122</v>
+      </c>
+      <c r="D374">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A375" s="1">
+        <v>46551</v>
+      </c>
+      <c r="B375">
+        <v>1221</v>
+      </c>
+      <c r="C375">
+        <v>1122</v>
+      </c>
+      <c r="D375">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A376" s="1">
+        <v>46552</v>
+      </c>
+      <c r="B376">
+        <v>1221</v>
+      </c>
+      <c r="C376">
+        <v>1122</v>
+      </c>
+      <c r="D376">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A377" s="1">
+        <v>46553</v>
+      </c>
+      <c r="B377">
+        <v>1221</v>
+      </c>
+      <c r="C377">
+        <v>1122</v>
+      </c>
+      <c r="D377">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A378" s="1">
+        <v>46554</v>
+      </c>
+      <c r="B378">
+        <v>1221</v>
+      </c>
+      <c r="C378">
+        <v>1122</v>
+      </c>
+      <c r="D378">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A379" s="1">
+        <v>46555</v>
+      </c>
+      <c r="B379">
+        <v>1221</v>
+      </c>
+      <c r="C379">
+        <v>1122</v>
+      </c>
+      <c r="D379">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A380" s="1">
+        <v>46556</v>
+      </c>
+      <c r="B380">
+        <v>1221</v>
+      </c>
+      <c r="C380">
+        <v>1122</v>
+      </c>
+      <c r="D380">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A381" s="1">
+        <v>46557</v>
+      </c>
+      <c r="B381">
+        <v>1221</v>
+      </c>
+      <c r="C381">
+        <v>1122</v>
+      </c>
+      <c r="D381">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A382" s="1">
+        <v>46558</v>
+      </c>
+      <c r="B382">
+        <v>1221</v>
+      </c>
+      <c r="C382">
+        <v>1122</v>
+      </c>
+      <c r="D382">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A383" s="1">
+        <v>46559</v>
+      </c>
+      <c r="B383">
+        <v>1221</v>
+      </c>
+      <c r="C383">
+        <v>1122</v>
+      </c>
+      <c r="D383">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A384" s="1">
+        <v>46560</v>
+      </c>
+      <c r="B384">
+        <v>1221</v>
+      </c>
+      <c r="C384">
+        <v>1122</v>
+      </c>
+      <c r="D384">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A385" s="1">
+        <v>46561</v>
+      </c>
+      <c r="B385">
+        <v>1221</v>
+      </c>
+      <c r="C385">
+        <v>1122</v>
+      </c>
+      <c r="D385">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A386" s="1">
+        <v>46562</v>
+      </c>
+      <c r="B386">
+        <v>1221</v>
+      </c>
+      <c r="C386">
+        <v>1122</v>
+      </c>
+      <c r="D386">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A387" s="1">
+        <v>46563</v>
+      </c>
+      <c r="B387">
+        <v>1221</v>
+      </c>
+      <c r="C387">
+        <v>1122</v>
+      </c>
+      <c r="D387">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A388" s="1">
+        <v>46564</v>
+      </c>
+      <c r="B388">
+        <v>1221</v>
+      </c>
+      <c r="C388">
+        <v>1122</v>
+      </c>
+      <c r="D388">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A389" s="1">
+        <v>46565</v>
+      </c>
+      <c r="B389">
+        <v>1221</v>
+      </c>
+      <c r="C389">
+        <v>1122</v>
+      </c>
+      <c r="D389">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A390" s="1">
+        <v>46566</v>
+      </c>
+      <c r="B390">
+        <v>1221</v>
+      </c>
+      <c r="C390">
+        <v>1122</v>
+      </c>
+      <c r="D390">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A391" s="1">
+        <v>46567</v>
+      </c>
+      <c r="B391">
+        <v>1221</v>
+      </c>
+      <c r="C391">
+        <v>1122</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A392" s="1">
+        <v>46568</v>
+      </c>
+      <c r="B392">
+        <v>1221</v>
+      </c>
+      <c r="C392">
+        <v>1122</v>
+      </c>
+      <c r="D392">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A393" s="1">
+        <v>46569</v>
+      </c>
+      <c r="B393">
+        <v>1221</v>
+      </c>
+      <c r="C393">
+        <v>1122</v>
+      </c>
+      <c r="D393">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A394" s="1">
+        <v>46570</v>
+      </c>
+      <c r="B394">
+        <v>1221</v>
+      </c>
+      <c r="C394">
+        <v>1122</v>
+      </c>
+      <c r="D394">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A395" s="1">
+        <v>46571</v>
+      </c>
+      <c r="B395">
+        <v>1221</v>
+      </c>
+      <c r="C395">
+        <v>1122</v>
+      </c>
+      <c r="D395">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A396" s="1">
+        <v>46572</v>
+      </c>
+      <c r="B396">
+        <v>1221</v>
+      </c>
+      <c r="C396">
+        <v>1122</v>
+      </c>
+      <c r="D396">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A397" s="1">
+        <v>46573</v>
+      </c>
+      <c r="B397">
+        <v>1221</v>
+      </c>
+      <c r="C397">
+        <v>1122</v>
+      </c>
+      <c r="D397">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A398" s="1">
+        <v>46574</v>
+      </c>
+      <c r="B398">
+        <v>1221</v>
+      </c>
+      <c r="C398">
+        <v>1122</v>
+      </c>
+      <c r="D398">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A399" s="1">
+        <v>46575</v>
+      </c>
+      <c r="B399">
+        <v>1221</v>
+      </c>
+      <c r="C399">
+        <v>1122</v>
+      </c>
+      <c r="D399">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A400" s="1">
+        <v>46576</v>
+      </c>
+      <c r="B400">
+        <v>1221</v>
+      </c>
+      <c r="C400">
+        <v>1122</v>
+      </c>
+      <c r="D400">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A401" s="1">
+        <v>46577</v>
+      </c>
+      <c r="B401">
+        <v>1221</v>
+      </c>
+      <c r="C401">
+        <v>1122</v>
+      </c>
+      <c r="D401">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A402" s="1">
+        <v>46578</v>
+      </c>
+      <c r="B402">
+        <v>1221</v>
+      </c>
+      <c r="C402">
+        <v>1122</v>
+      </c>
+      <c r="D402">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A403" s="1">
+        <v>46579</v>
+      </c>
+      <c r="B403">
+        <v>1221</v>
+      </c>
+      <c r="C403">
+        <v>1122</v>
+      </c>
+      <c r="D403">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A404" s="1">
+        <v>46580</v>
+      </c>
+      <c r="B404">
+        <v>1221</v>
+      </c>
+      <c r="C404">
+        <v>1122</v>
+      </c>
+      <c r="D404">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A405" s="1">
+        <v>46581</v>
+      </c>
+      <c r="B405">
+        <v>1221</v>
+      </c>
+      <c r="C405">
+        <v>1122</v>
+      </c>
+      <c r="D405">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A406" s="1">
+        <v>46582</v>
+      </c>
+      <c r="B406">
+        <v>1221</v>
+      </c>
+      <c r="C406">
+        <v>1122</v>
+      </c>
+      <c r="D406">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A407" s="1">
+        <v>46583</v>
+      </c>
+      <c r="B407">
+        <v>1221</v>
+      </c>
+      <c r="C407">
+        <v>1122</v>
+      </c>
+      <c r="D407">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A408" s="1">
+        <v>46584</v>
+      </c>
+      <c r="B408">
+        <v>1221</v>
+      </c>
+      <c r="C408">
+        <v>1122</v>
+      </c>
+      <c r="D408">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A409" s="1">
+        <v>46585</v>
+      </c>
+      <c r="B409">
+        <v>1221</v>
+      </c>
+      <c r="C409">
+        <v>1122</v>
+      </c>
+      <c r="D409">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A410" s="1">
+        <v>46586</v>
+      </c>
+      <c r="B410">
+        <v>1221</v>
+      </c>
+      <c r="C410">
+        <v>1122</v>
+      </c>
+      <c r="D410">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A411" s="1">
+        <v>46587</v>
+      </c>
+      <c r="B411">
+        <v>1221</v>
+      </c>
+      <c r="C411">
+        <v>1122</v>
+      </c>
+      <c r="D411">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A412" s="1">
+        <v>46588</v>
+      </c>
+      <c r="B412">
+        <v>1221</v>
+      </c>
+      <c r="C412">
+        <v>1122</v>
+      </c>
+      <c r="D412">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A413" s="1">
+        <v>46589</v>
+      </c>
+      <c r="B413">
+        <v>1221</v>
+      </c>
+      <c r="C413">
+        <v>1122</v>
+      </c>
+      <c r="D413">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A414" s="1">
+        <v>46590</v>
+      </c>
+      <c r="B414">
+        <v>1221</v>
+      </c>
+      <c r="C414">
+        <v>1122</v>
+      </c>
+      <c r="D414">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A415" s="1">
+        <v>46591</v>
+      </c>
+      <c r="B415">
+        <v>1221</v>
+      </c>
+      <c r="C415">
+        <v>1122</v>
+      </c>
+      <c r="D415">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A416" s="1">
+        <v>46592</v>
+      </c>
+      <c r="B416">
+        <v>1221</v>
+      </c>
+      <c r="C416">
+        <v>1122</v>
+      </c>
+      <c r="D416">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A417" s="1">
+        <v>46593</v>
+      </c>
+      <c r="B417">
+        <v>1221</v>
+      </c>
+      <c r="C417">
+        <v>1122</v>
+      </c>
+      <c r="D417">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A418" s="1">
+        <v>46594</v>
+      </c>
+      <c r="B418">
+        <v>1221</v>
+      </c>
+      <c r="C418">
+        <v>1122</v>
+      </c>
+      <c r="D418">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A419" s="1">
+        <v>46595</v>
+      </c>
+      <c r="B419">
+        <v>1221</v>
+      </c>
+      <c r="C419">
+        <v>1122</v>
+      </c>
+      <c r="D419">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A420" s="1">
+        <v>46596</v>
+      </c>
+      <c r="B420">
+        <v>1221</v>
+      </c>
+      <c r="C420">
+        <v>1122</v>
+      </c>
+      <c r="D420">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A421" s="1">
+        <v>46597</v>
+      </c>
+      <c r="B421">
+        <v>1221</v>
+      </c>
+      <c r="C421">
+        <v>1122</v>
+      </c>
+      <c r="D421">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A422" s="1">
+        <v>46598</v>
+      </c>
+      <c r="B422">
+        <v>1221</v>
+      </c>
+      <c r="C422">
+        <v>1122</v>
+      </c>
+      <c r="D422">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A423" s="1">
+        <v>46599</v>
+      </c>
+      <c r="B423">
+        <v>1221</v>
+      </c>
+      <c r="C423">
+        <v>1122</v>
+      </c>
+      <c r="D423">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A424" s="1">
+        <v>46600</v>
+      </c>
+      <c r="B424">
+        <v>1221</v>
+      </c>
+      <c r="C424">
+        <v>1122</v>
+      </c>
+      <c r="D424">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A425" s="1">
+        <v>46601</v>
+      </c>
+      <c r="B425">
+        <v>1221</v>
+      </c>
+      <c r="C425">
+        <v>1122</v>
+      </c>
+      <c r="D425">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A426" s="1">
+        <v>46602</v>
+      </c>
+      <c r="B426">
+        <v>1221</v>
+      </c>
+      <c r="C426">
+        <v>1122</v>
+      </c>
+      <c r="D426">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A427" s="1">
+        <v>46603</v>
+      </c>
+      <c r="B427">
+        <v>1221</v>
+      </c>
+      <c r="C427">
+        <v>1122</v>
+      </c>
+      <c r="D427">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A428" s="1">
+        <v>46604</v>
+      </c>
+      <c r="B428">
+        <v>1221</v>
+      </c>
+      <c r="C428">
+        <v>1122</v>
+      </c>
+      <c r="D428">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A429" s="1">
+        <v>46605</v>
+      </c>
+      <c r="B429">
+        <v>1221</v>
+      </c>
+      <c r="C429">
+        <v>1122</v>
+      </c>
+      <c r="D429">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A430" s="1">
+        <v>46606</v>
+      </c>
+      <c r="B430">
+        <v>1221</v>
+      </c>
+      <c r="C430">
+        <v>1122</v>
+      </c>
+      <c r="D430">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A431" s="1">
+        <v>46607</v>
+      </c>
+      <c r="B431">
+        <v>1221</v>
+      </c>
+      <c r="C431">
+        <v>1122</v>
+      </c>
+      <c r="D431">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A432" s="1">
+        <v>46608</v>
+      </c>
+      <c r="B432">
+        <v>1221</v>
+      </c>
+      <c r="C432">
+        <v>1122</v>
+      </c>
+      <c r="D432">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A433" s="1">
+        <v>46609</v>
+      </c>
+      <c r="B433">
+        <v>1221</v>
+      </c>
+      <c r="C433">
+        <v>1122</v>
+      </c>
+      <c r="D433">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A434" s="1">
+        <v>46610</v>
+      </c>
+      <c r="B434">
+        <v>1221</v>
+      </c>
+      <c r="C434">
+        <v>1122</v>
+      </c>
+      <c r="D434">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A435" s="1">
+        <v>46611</v>
+      </c>
+      <c r="B435">
+        <v>1221</v>
+      </c>
+      <c r="C435">
+        <v>1122</v>
+      </c>
+      <c r="D435">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A436" s="1">
+        <v>46612</v>
+      </c>
+      <c r="B436">
+        <v>1221</v>
+      </c>
+      <c r="C436">
+        <v>1122</v>
+      </c>
+      <c r="D436">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A437" s="1">
+        <v>46613</v>
+      </c>
+      <c r="B437">
+        <v>1221</v>
+      </c>
+      <c r="C437">
+        <v>1122</v>
+      </c>
+      <c r="D437">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A438" s="1">
+        <v>46614</v>
+      </c>
+      <c r="B438">
+        <v>1221</v>
+      </c>
+      <c r="C438">
+        <v>1122</v>
+      </c>
+      <c r="D438">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A439" s="1">
+        <v>46615</v>
+      </c>
+      <c r="B439">
+        <v>1221</v>
+      </c>
+      <c r="C439">
+        <v>1122</v>
+      </c>
+      <c r="D439">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A440" s="1">
+        <v>46616</v>
+      </c>
+      <c r="B440">
+        <v>1221</v>
+      </c>
+      <c r="C440">
+        <v>1122</v>
+      </c>
+      <c r="D440">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A441" s="1">
+        <v>46617</v>
+      </c>
+      <c r="B441">
+        <v>1221</v>
+      </c>
+      <c r="C441">
+        <v>1122</v>
+      </c>
+      <c r="D441">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A442" s="1">
+        <v>46618</v>
+      </c>
+      <c r="B442">
+        <v>1221</v>
+      </c>
+      <c r="C442">
+        <v>1122</v>
+      </c>
+      <c r="D442">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A443" s="1">
+        <v>46619</v>
+      </c>
+      <c r="B443">
+        <v>1221</v>
+      </c>
+      <c r="C443">
+        <v>1122</v>
+      </c>
+      <c r="D443">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A444" s="1">
+        <v>46620</v>
+      </c>
+      <c r="B444">
+        <v>1221</v>
+      </c>
+      <c r="C444">
+        <v>1122</v>
+      </c>
+      <c r="D444">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A445" s="1">
+        <v>46621</v>
+      </c>
+      <c r="B445">
+        <v>1221</v>
+      </c>
+      <c r="C445">
+        <v>1122</v>
+      </c>
+      <c r="D445">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A446" s="1">
+        <v>46622</v>
+      </c>
+      <c r="B446">
+        <v>1221</v>
+      </c>
+      <c r="C446">
+        <v>1122</v>
+      </c>
+      <c r="D446">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A447" s="1">
+        <v>46623</v>
+      </c>
+      <c r="B447">
+        <v>1221</v>
+      </c>
+      <c r="C447">
+        <v>1122</v>
+      </c>
+      <c r="D447">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A448" s="1">
+        <v>46624</v>
+      </c>
+      <c r="B448">
+        <v>1221</v>
+      </c>
+      <c r="C448">
+        <v>1122</v>
+      </c>
+      <c r="D448">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A449" s="1">
+        <v>46625</v>
+      </c>
+      <c r="B449">
+        <v>1221</v>
+      </c>
+      <c r="C449">
+        <v>1122</v>
+      </c>
+      <c r="D449">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A450" s="1">
+        <v>46626</v>
+      </c>
+      <c r="B450">
+        <v>1221</v>
+      </c>
+      <c r="C450">
+        <v>1122</v>
+      </c>
+      <c r="D450">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A451" s="1">
+        <v>46627</v>
+      </c>
+      <c r="B451">
+        <v>1221</v>
+      </c>
+      <c r="C451">
+        <v>1122</v>
+      </c>
+      <c r="D451">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A452" s="1">
+        <v>46628</v>
+      </c>
+      <c r="B452">
+        <v>1221</v>
+      </c>
+      <c r="C452">
+        <v>1122</v>
+      </c>
+      <c r="D452">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A453" s="1">
+        <v>46629</v>
+      </c>
+      <c r="B453">
+        <v>1221</v>
+      </c>
+      <c r="C453">
+        <v>1122</v>
+      </c>
+      <c r="D453">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A454" s="1">
+        <v>46630</v>
+      </c>
+      <c r="B454">
+        <v>1221</v>
+      </c>
+      <c r="C454">
+        <v>1122</v>
+      </c>
+      <c r="D454">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A455" s="1">
+        <v>46631</v>
+      </c>
+      <c r="B455">
+        <v>1221</v>
+      </c>
+      <c r="C455">
+        <v>1122</v>
+      </c>
+      <c r="D455">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A456" s="1">
+        <v>46632</v>
+      </c>
+      <c r="B456">
+        <v>1221</v>
+      </c>
+      <c r="C456">
+        <v>1122</v>
+      </c>
+      <c r="D456">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A457" s="1">
+        <v>46633</v>
+      </c>
+      <c r="B457">
+        <v>1221</v>
+      </c>
+      <c r="C457">
+        <v>1122</v>
+      </c>
+      <c r="D457">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A458" s="1">
+        <v>46634</v>
+      </c>
+      <c r="B458">
+        <v>1221</v>
+      </c>
+      <c r="C458">
+        <v>1122</v>
+      </c>
+      <c r="D458">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A459" s="1">
+        <v>46635</v>
+      </c>
+      <c r="B459">
+        <v>1221</v>
+      </c>
+      <c r="C459">
+        <v>1122</v>
+      </c>
+      <c r="D459">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A460" s="1">
+        <v>46636</v>
+      </c>
+      <c r="B460">
+        <v>1221</v>
+      </c>
+      <c r="C460">
+        <v>1122</v>
+      </c>
+      <c r="D460">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A461" s="1">
+        <v>46637</v>
+      </c>
+      <c r="B461">
+        <v>1221</v>
+      </c>
+      <c r="C461">
+        <v>1122</v>
+      </c>
+      <c r="D461">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A462" s="1">
+        <v>46638</v>
+      </c>
+      <c r="B462">
+        <v>1221</v>
+      </c>
+      <c r="C462">
+        <v>1122</v>
+      </c>
+      <c r="D462">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A463" s="1">
+        <v>46639</v>
+      </c>
+      <c r="B463">
+        <v>1221</v>
+      </c>
+      <c r="C463">
+        <v>1122</v>
+      </c>
+      <c r="D463">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A464" s="1">
+        <v>46640</v>
+      </c>
+      <c r="B464">
+        <v>1221</v>
+      </c>
+      <c r="C464">
+        <v>1122</v>
+      </c>
+      <c r="D464">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A465" s="1">
+        <v>46641</v>
+      </c>
+      <c r="B465">
+        <v>1221</v>
+      </c>
+      <c r="C465">
+        <v>1122</v>
+      </c>
+      <c r="D465">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A466" s="1">
+        <v>46642</v>
+      </c>
+      <c r="B466">
+        <v>1221</v>
+      </c>
+      <c r="C466">
+        <v>1122</v>
+      </c>
+      <c r="D466">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A467" s="1">
+        <v>46643</v>
+      </c>
+      <c r="B467">
+        <v>1221</v>
+      </c>
+      <c r="C467">
+        <v>1122</v>
+      </c>
+      <c r="D467">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A468" s="1">
+        <v>46644</v>
+      </c>
+      <c r="B468">
+        <v>1221</v>
+      </c>
+      <c r="C468">
+        <v>1122</v>
+      </c>
+      <c r="D468">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A469" s="1">
+        <v>46645</v>
+      </c>
+      <c r="B469">
+        <v>1221</v>
+      </c>
+      <c r="C469">
+        <v>1122</v>
+      </c>
+      <c r="D469">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A470" s="1">
+        <v>46646</v>
+      </c>
+      <c r="B470">
+        <v>1221</v>
+      </c>
+      <c r="C470">
+        <v>1122</v>
+      </c>
+      <c r="D470">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A471" s="1">
+        <v>46647</v>
+      </c>
+      <c r="B471">
+        <v>1221</v>
+      </c>
+      <c r="C471">
+        <v>1122</v>
+      </c>
+      <c r="D471">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A472" s="1">
+        <v>46648</v>
+      </c>
+      <c r="B472">
+        <v>1221</v>
+      </c>
+      <c r="C472">
+        <v>1122</v>
+      </c>
+      <c r="D472">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A473" s="1">
+        <v>46649</v>
+      </c>
+      <c r="B473">
+        <v>1221</v>
+      </c>
+      <c r="C473">
+        <v>1122</v>
+      </c>
+      <c r="D473">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A474" s="1">
+        <v>46650</v>
+      </c>
+      <c r="B474">
+        <v>1221</v>
+      </c>
+      <c r="C474">
+        <v>1122</v>
+      </c>
+      <c r="D474">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A475" s="1">
+        <v>46651</v>
+      </c>
+      <c r="B475">
+        <v>1221</v>
+      </c>
+      <c r="C475">
+        <v>1122</v>
+      </c>
+      <c r="D475">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A476" s="1">
+        <v>46652</v>
+      </c>
+      <c r="B476">
+        <v>1221</v>
+      </c>
+      <c r="C476">
+        <v>1122</v>
+      </c>
+      <c r="D476">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A477" s="1">
+        <v>46653</v>
+      </c>
+      <c r="B477">
+        <v>1221</v>
+      </c>
+      <c r="C477">
+        <v>1122</v>
+      </c>
+      <c r="D477">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A478" s="1">
+        <v>46654</v>
+      </c>
+      <c r="B478">
+        <v>1221</v>
+      </c>
+      <c r="C478">
+        <v>1122</v>
+      </c>
+      <c r="D478">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A479" s="1">
+        <v>46655</v>
+      </c>
+      <c r="B479">
+        <v>1221</v>
+      </c>
+      <c r="C479">
+        <v>1122</v>
+      </c>
+      <c r="D479">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A480" s="1">
+        <v>46656</v>
+      </c>
+      <c r="B480">
+        <v>1221</v>
+      </c>
+      <c r="C480">
+        <v>1122</v>
+      </c>
+      <c r="D480">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A481" s="1">
+        <v>46657</v>
+      </c>
+      <c r="B481">
+        <v>1221</v>
+      </c>
+      <c r="C481">
+        <v>1122</v>
+      </c>
+      <c r="D481">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A482" s="1">
+        <v>46658</v>
+      </c>
+      <c r="B482">
+        <v>1221</v>
+      </c>
+      <c r="C482">
+        <v>1122</v>
+      </c>
+      <c r="D482">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A483" s="1">
+        <v>46659</v>
+      </c>
+      <c r="B483">
+        <v>1221</v>
+      </c>
+      <c r="C483">
+        <v>1122</v>
+      </c>
+      <c r="D483">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A484" s="1">
+        <v>46660</v>
+      </c>
+      <c r="B484">
+        <v>1221</v>
+      </c>
+      <c r="C484">
+        <v>1122</v>
+      </c>
+      <c r="D484">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A485" s="1">
+        <v>46661</v>
+      </c>
+      <c r="B485">
+        <v>1221</v>
+      </c>
+      <c r="C485">
+        <v>1122</v>
+      </c>
+      <c r="D485">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A486" s="1">
+        <v>46662</v>
+      </c>
+      <c r="B486">
+        <v>1221</v>
+      </c>
+      <c r="C486">
+        <v>1122</v>
+      </c>
+      <c r="D486">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A487" s="1">
+        <v>46663</v>
+      </c>
+      <c r="B487">
+        <v>1221</v>
+      </c>
+      <c r="C487">
+        <v>1122</v>
+      </c>
+      <c r="D487">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A488" s="1">
+        <v>46664</v>
+      </c>
+      <c r="B488">
+        <v>1221</v>
+      </c>
+      <c r="C488">
+        <v>1122</v>
+      </c>
+      <c r="D488">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A489" s="1">
+        <v>46665</v>
+      </c>
+      <c r="B489">
+        <v>1221</v>
+      </c>
+      <c r="C489">
+        <v>1122</v>
+      </c>
+      <c r="D489">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A490" s="1">
+        <v>46666</v>
+      </c>
+      <c r="B490">
+        <v>1221</v>
+      </c>
+      <c r="C490">
+        <v>1122</v>
+      </c>
+      <c r="D490">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A491" s="1">
+        <v>46667</v>
+      </c>
+      <c r="B491">
+        <v>1221</v>
+      </c>
+      <c r="C491">
+        <v>1122</v>
+      </c>
+      <c r="D491">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A492" s="1">
+        <v>46668</v>
+      </c>
+      <c r="B492">
+        <v>1221</v>
+      </c>
+      <c r="C492">
+        <v>1122</v>
+      </c>
+      <c r="D492">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
